--- a/src/attributions/attributions_ig_traj_382.xlsx
+++ b/src/attributions/attributions_ig_traj_382.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07771974244017646</v>
+        <v>0.03454792424769294</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0008394893931818036</v>
+        <v>-0.008903319413345847</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.453275649002179e-11</v>
+        <v>-2.250581116552067e-11</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07113984708622841</v>
+        <v>0.05920251468393428</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.009951721881363281</v>
+        <v>-0.02033537915888503</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,70 +1047,70 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03738878207630252</v>
+        <v>-0.009598452904239463</v>
       </c>
       <c r="S2" t="n">
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09833266649182555</v>
+        <v>0.02381358350450472</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1399135991528329</v>
+        <v>-0.06155045652202686</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03248941239911798</v>
+        <v>-0.01792416561364418</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1245036174954221</v>
+        <v>-0.03718878481047451</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1324076821177878</v>
+        <v>-0.07259396222793102</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0002509231729045524</v>
+        <v>0.04397620934279371</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0685255760390568</v>
+        <v>0.03352964295025788</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,34 +1119,34 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.005572740617587797</v>
+        <v>-0.02596719764464784</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.04981845297379925</v>
+        <v>-0.002594562401575602</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4973158039296633</v>
+        <v>0.304335795812783</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3407022947796501</v>
+        <v>-0.09893431214261078</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.07369214141055512</v>
+        <v>-0.03099165901442079</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.00134728552182213</v>
+        <v>-0.02434296645327677</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,61 +1173,61 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.1083530818269705</v>
+        <v>-0.03877387502150325</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.2051739586666704</v>
+        <v>-0.05395628398808022</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.1041886225752398</v>
+        <v>0.03399290584867319</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2756845253634328</v>
+        <v>0.1121765766161558</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1118927298255811</v>
+        <v>0.04453232941737414</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2370949167552503</v>
+        <v>0.1168751107221481</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.05516907166762414</v>
+        <v>-0.04570520664122425</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,55 +1236,55 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05318595136813508</v>
+        <v>-0.02953354100179495</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1057525566966706</v>
+        <v>-0.07632827684649149</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.009068954411626133</v>
+        <v>0.01994438059661168</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.08586379102335101</v>
+        <v>0.03330716315684647</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.001839453523586206</v>
+        <v>0.01203975450006704</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03316678017980796</v>
+        <v>-0.002068426525243242</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,40 +1293,40 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.02161337275213312</v>
+        <v>-0.009700136726880708</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1119237723195248</v>
+        <v>-0.07296415989427915</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.004822838288012991</v>
+        <v>0.008961726619851496</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.06198815840565686</v>
+        <v>0.03248466982734308</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1238003740548136</v>
+        <v>-0.08393682277984454</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
@@ -1335,64 +1335,64 @@
         <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.02611834041799521</v>
+        <v>0.004340502184320538</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0.02785324449381073</v>
+        <v>0.002943923784477674</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.03690672132084897</v>
+        <v>-0.02258279984993279</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.08547530616381106</v>
+        <v>0.03441021005798962</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.05883508826086538</v>
+        <v>0.0365194373033667</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.18109167865787</v>
+        <v>-0.07584716885110167</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.07850166768680578</v>
+        <v>0.02048172798517435</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.03767590477579693</v>
+        <v>-0.01110548116957769</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.05911857552138346</v>
+        <v>-0.04175518412951608</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.02315437766523882</v>
+        <v>-0.03480225161085158</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,70 +1425,70 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1171021693311208</v>
+        <v>0.03584164206671785</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.03728786678714628</v>
+        <v>-0.01125017937451258</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03639949225023702</v>
+        <v>-0.004515786517435361</v>
       </c>
       <c r="ET2" t="n">
         <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.09091596083488743</v>
+        <v>0.04295931520008203</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1186727053045456</v>
+        <v>-0.09629743084269929</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.005320494582858814</v>
+        <v>0.01103054054124069</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.06999654792859387</v>
+        <v>0.02785197593200874</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.04065818144897042</v>
+        <v>0.05587909597643758</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,7 +1497,7 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1720977755483251</v>
+        <v>0.01423551650951494</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1509,40 +1509,40 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.02977652568923146</v>
+        <v>0.05481818431751229</v>
       </c>
       <c r="FP2" t="n">
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.02884824310227984</v>
+        <v>-0.008095805961106504</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.01376581407068548</v>
+        <v>0.01056777740624991</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.0178227562636166</v>
+        <v>-0.002744704588753089</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.079171507900268</v>
+        <v>-0.04483211861609308</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.06654552025759038</v>
+        <v>0.00204223358146583</v>
       </c>
     </row>
     <row r="3">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1677222877244371</v>
+        <v>0.002649007870478002</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0327042510192893</v>
+        <v>6.414080892349501e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.03455669806448274</v>
+        <v>-0.0001303896110538552</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2733,28 +2733,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1104211512453711</v>
+        <v>0.004117890680458409</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03112645986679418</v>
+        <v>0.0003342953938237975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03801102430741406</v>
+        <v>-0.0006992225776128342</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,79 +2763,79 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1394063996864389</v>
+        <v>-0.001158623973615214</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1349900043221854</v>
+        <v>-0.004255079095193466</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.02231609730691417</v>
+        <v>0.000796382304202752</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1866121852378174</v>
+        <v>-0.004666426372016985</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05912136986258744</v>
+        <v>-0.004979797764650298</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.02165734130402213</v>
+        <v>-0.002197694900042079</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.05932671443403451</v>
+        <v>0.002339471552592591</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.05960317442563767</v>
+        <v>-0.0003156284532668506</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.05660012868453931</v>
+        <v>-0.0004305189938578798</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,34 +2844,34 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4656460995401648</v>
+        <v>0.01611654667035782</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2686379589337212</v>
+        <v>0.0003731200980430064</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2110991981397806</v>
+        <v>4.04393828745478e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02972875774035636</v>
+        <v>-0.003832048724570988</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,16 +2880,16 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1581919267955882</v>
+        <v>-0.003695417785314239</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.02300312556943029</v>
+        <v>-0.001021137193548351</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,22 +2898,22 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.06789962422519748</v>
+        <v>0.002395154704872183</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.03275835545947256</v>
+        <v>0.006339138392549967</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1264031911903932</v>
+        <v>-0.0018910928500881</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,118 +2922,118 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1853818313211798</v>
+        <v>0.006677561487627445</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.09456432137888263</v>
+        <v>0.0006943969539473464</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.07326246729326286</v>
+        <v>-0.0002742390145249461</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1146734335562387</v>
+        <v>-0.002241126185324517</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.04535192928386758</v>
+        <v>-0.0004543539080076151</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.05402807083118573</v>
+        <v>0.0007195640040066816</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.003173719609056883</v>
+        <v>-0.000425653023543775</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.001875159542348816</v>
+        <v>-2.078599827041073e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001868527591365594</v>
+        <v>-0.0001319283981992466</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1177110075296426</v>
+        <v>-0.002308201817469311</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.06473982296810883</v>
+        <v>-0.0009159860430842967</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.07323013407568554</v>
+        <v>0.001035907993690986</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1406827285505805</v>
+        <v>-0.00299208938138522</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.04060867609681155</v>
+        <v>-0.003403267018053427</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.03611759989375857</v>
+        <v>-0.001643724269814232</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
@@ -3057,64 +3057,64 @@
         <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01237215272148373</v>
+        <v>0.0007724194729817347</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.06433826117167507</v>
+        <v>0.0007179691046711681</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.02354357101408794</v>
+        <v>0.004514485868995933</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1522480406126855</v>
+        <v>-0.001580927494851193</v>
       </c>
       <c r="DY5" t="n">
         <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.0276869717422973</v>
+        <v>-0.003009781620474644</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01950303140720212</v>
+        <v>0.001428997192050011</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.05019131859046035</v>
+        <v>-0.003011761499507539</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
@@ -3123,40 +3123,40 @@
         <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.006881465928629336</v>
+        <v>-0.001416785251017268</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.08944808262138233</v>
+        <v>-0.0006792234638169425</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1109486688996904</v>
+        <v>-0.001402276738990949</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1395630091911578</v>
+        <v>0.001112537595464356</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.04834604388470879</v>
+        <v>0.003816649452042671</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1217415510102037</v>
+        <v>-0.003309021249736447</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,25 +3177,25 @@
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.08660262112781281</v>
+        <v>-0.001679087745719285</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.07459067336235482</v>
+        <v>0.0007202110989976887</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01763553691651098</v>
+        <v>0.002872221012881295</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
@@ -3204,67 +3204,67 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.07002077484042891</v>
+        <v>-0.0003345714826527816</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.005105175845228778</v>
+        <v>0.0008345655366736014</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01632186323217343</v>
+        <v>-0.0002128368384646312</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.004369849189075988</v>
+        <v>-0.0001203510551575343</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.05402740940908083</v>
+        <v>0.001769355678423706</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.06325942339508675</v>
+        <v>-0.002050073702218995</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.03784409909874745</v>
+        <v>0.001896572935242301</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
@@ -3844,19 +3844,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.2767830536678095</v>
+        <v>-0.1086524855833301</v>
       </c>
       <c r="C7" t="n">
         <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3799092718109449</v>
+        <v>0.1637376927750149</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03747543123700743</v>
+        <v>0.01404650269449125</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -3871,25 +3871,25 @@
         <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3252711825415885</v>
+        <v>-0.1767572856184386</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.320645874741922</v>
+        <v>0.1744607280812146</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05376425233994862</v>
+        <v>0.0214489851526608</v>
       </c>
       <c r="O7" t="n">
         <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0</v>
@@ -3901,22 +3901,22 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2756507670719556</v>
+        <v>-0.1207198102182421</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1369499765679365</v>
+        <v>0.03827237725156835</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1660534927517974</v>
+        <v>0.0239097766518069</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,25 +3925,25 @@
         <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.2804672819143934</v>
+        <v>0.08363410287522317</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1796304842867247</v>
+        <v>0.2509966556766686</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.179589669648885</v>
+        <v>-0.02346275663130163</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3952,79 +3952,79 @@
         <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.09225819290708483</v>
+        <v>-0.1441013441602466</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.03970411026576549</v>
+        <v>0.09532420043830162</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.06801925360123998</v>
+        <v>-0.1495440223855403</v>
       </c>
       <c r="AP7" t="n">
         <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.9764504651976478</v>
+        <v>-0.470372019516282</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2867169121878131</v>
+        <v>0.2411982479053766</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.09079408004578123</v>
+        <v>0.1084535892364334</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.2100997295600116</v>
+        <v>0.03790285665570337</v>
       </c>
       <c r="BE7" t="n">
         <v>-0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.3943823229923711</v>
+        <v>0.07261686540578495</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.348076119610016</v>
+        <v>0.04224865472904057</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>-0</v>
@@ -4033,28 +4033,28 @@
         <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.06647261811766515</v>
+        <v>0.08121338555951473</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.04742203825425054</v>
+        <v>-0.02699843135169103</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.2359034087380709</v>
+        <v>-0.04523580868729733</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
@@ -4063,22 +4063,22 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.4254894582154978</v>
+        <v>-0.3125200859582754</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.2052624551674694</v>
+        <v>0.1498971954050109</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.1892456210217238</v>
+        <v>0.02843056224193002</v>
       </c>
       <c r="BZ7" t="n">
         <v>-0</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
@@ -4090,22 +4090,22 @@
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.2292116235662202</v>
+        <v>0.1663592736242348</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.1401123504516207</v>
+        <v>-0.1638862244535464</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.02265130317909805</v>
+        <v>0.005657953770856001</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK7" t="n">
         <v>-0</v>
@@ -4117,16 +4117,16 @@
         <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.004763864300050668</v>
+        <v>0.02132711301709451</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0005979529183129748</v>
+        <v>-0.05105543122251719</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.007406110857862727</v>
+        <v>-0.01381053518593688</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
@@ -4141,25 +4141,25 @@
         <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.2182310038153999</v>
+        <v>0.1725917236180895</v>
       </c>
       <c r="CX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.1748289800010102</v>
+        <v>-0.1630146261917687</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.008595518089741993</v>
+        <v>-0.02054526207651787</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
@@ -4171,22 +4171,22 @@
         <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.3690975733931592</v>
+        <v>0.2862152090406841</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.199753442582372</v>
+        <v>-0.09415185210698945</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1128692297070396</v>
+        <v>0.08649654823944602</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL7" t="n">
         <v>-0</v>
@@ -4195,28 +4195,28 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.07677994392570058</v>
+        <v>0.05094884902702691</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.0419432914338053</v>
+        <v>-0.06504185709694661</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2027074659784759</v>
+        <v>0.01669598843406084</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.05019959566182534</v>
+        <v>-0.04140466145272553</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.1730165582600978</v>
+        <v>0.138387456020143</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.1362145194885371</v>
+        <v>0.1984085339873438</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED7" t="n">
         <v>-0</v>
@@ -4249,49 +4249,49 @@
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.1593645123736472</v>
+        <v>0.1302020759760639</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.08782229405332637</v>
+        <v>-0.109210785643912</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.1525059771242575</v>
+        <v>-0.05975748982535078</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.1764015999865561</v>
+        <v>0.09766306877921359</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.08204433590105971</v>
+        <v>-0.08874495134792509</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1214987865025624</v>
+        <v>0.0171106703719947</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU7" t="n">
         <v>-0</v>
@@ -4306,43 +4306,43 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2349809012500765</v>
+        <v>0.1886582284032815</v>
       </c>
       <c r="EZ7" t="n">
         <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.1666139476062326</v>
+        <v>-0.1939260878860931</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01460061298893193</v>
+        <v>0.01249843539682419</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
         <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.1626726997370623</v>
+        <v>0.1678050846205571</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.06643290349958256</v>
+        <v>-0.09921847767278698</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.08791028815963535</v>
+        <v>0.1207343604696813</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,25 +4351,25 @@
         <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.02308596507874988</v>
+        <v>0.02940401238573957</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.1315192601148695</v>
+        <v>-0.154421396352305</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.01363827957059044</v>
+        <v>-0.01667037691380875</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4381,25 +4381,25 @@
         <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.04350891015863213</v>
+        <v>0.192972427690349</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.1516289964340456</v>
+        <v>-0.1157708760292475</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE7" t="n">
         <v>0</v>
@@ -4413,19 +4413,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2096069216889178</v>
+        <v>0.2851957101299882</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02450466850426231</v>
+        <v>-0.0493847145850418</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01801446947217267</v>
+        <v>-0.06902896183946958</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4434,25 +4434,25 @@
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.132614668568887</v>
+        <v>0.2497756333178141</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.032914598163207</v>
+        <v>-0.1031580364669724</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0282139544355452</v>
+        <v>-0.09157449607174192</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4461,28 +4461,28 @@
         <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09562744900909066</v>
+        <v>0.1333125565051399</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.03843231011639562</v>
+        <v>0.01756898781325637</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00585641882614002</v>
+        <v>-0.0754298694895862</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
@@ -4494,25 +4494,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0402512152060662</v>
+        <v>0.02850118712937215</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01129906907090261</v>
+        <v>-0.1134129041608806</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.0432070840563173</v>
+        <v>-0.06648710020330142</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,73 +4521,73 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02371063510111156</v>
+        <v>0.1882117645276966</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.03512072505346207</v>
+        <v>0.01332145224720794</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.03819811612057914</v>
+        <v>0.07307447006426544</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4126962863485064</v>
+        <v>0.4993583390834092</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.05294361989511844</v>
+        <v>-0.2274786531167796</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1098091289330707</v>
+        <v>-0.2365522348175307</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0334330599135737</v>
+        <v>0.007900204212938886</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.05842123365967383</v>
+        <v>-0.08856657960872923</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1414831060173009</v>
+        <v>-0.04071809864178897</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4596,31 +4596,31 @@
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.06724624236212798</v>
+        <v>-0.04420506813487</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.08207997456415107</v>
+        <v>0.07039571197713182</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.09004490878156127</v>
+        <v>0.1288099691040524</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,43 +4632,43 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2128172577124213</v>
+        <v>0.3558235949161911</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.01864343637505053</v>
+        <v>-0.1440578696236396</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03695431420848111</v>
+        <v>-0.08410195256668106</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.08430185155539791</v>
+        <v>-0.1865058512285356</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.03503232660836136</v>
+        <v>0.1478855860197128</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02348506752332631</v>
+        <v>0.02508657301684612</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
@@ -4680,25 +4680,25 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.004270341452961518</v>
+        <v>-0.03946050029490732</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.01320263479841137</v>
+        <v>-0.02767731307066326</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.02041469797774862</v>
+        <v>0.009190704410747829</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4710,49 +4710,49 @@
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.07838395602790869</v>
+        <v>-0.2031445658750529</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.05170569048694643</v>
+        <v>0.1494351637429649</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02450826371505874</v>
+        <v>0.03495766985157423</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.04847581256591235</v>
+        <v>-0.1374719973994522</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1368128329195364</v>
+        <v>0.1121121535638662</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.001783830134542337</v>
+        <v>-0.04855870858114952</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
         <v>-0</v>
@@ -4767,25 +4767,25 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.07693546359015081</v>
+        <v>-0.1263241475413226</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.02180769810119422</v>
+        <v>0.1051435927237061</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.01184283182591983</v>
+        <v>-0.07760828871385028</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,22 +4794,22 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.005187791879287321</v>
+        <v>0.07438407569058207</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.03383338189294984</v>
+        <v>0.1217913906606366</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01981965564382095</v>
+        <v>-0.05327627961082439</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.07888343429340283</v>
+        <v>-0.1092726049038844</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.07414952389426105</v>
+        <v>-0.1799435690384661</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01737463918468976</v>
+        <v>0.03915541686123006</v>
       </c>
       <c r="EK8" t="n">
         <v>-0</v>
@@ -4839,7 +4839,7 @@
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
@@ -4848,22 +4848,22 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.08612409710515377</v>
+        <v>-0.16307597808979</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.05571821815698814</v>
+        <v>0.0791507924776207</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.03309987846412531</v>
+        <v>-0.02767153153274204</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,49 +4875,49 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.07895533791240067</v>
+        <v>-0.2220964081610575</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.05959705965534372</v>
+        <v>0.1574799956425676</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03258040776868001</v>
+        <v>0.02085866902906373</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.00669127930228946</v>
+        <v>-0.05420718847554794</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.01653514493641941</v>
+        <v>-0.09060995914616934</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.01075033793708417</v>
+        <v>0.07435593457631423</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
         <v>-0</v>
@@ -4926,19 +4926,19 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.002780481248959557</v>
+        <v>-0.1026206856998609</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.05002826478514526</v>
+        <v>0.3367271695589202</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.056339080157495</v>
+        <v>0.1221238871378644</v>
       </c>
       <c r="FU8" t="n">
         <v>-0</v>
@@ -4953,28 +4953,28 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02572311096161309</v>
+        <v>-0.1465155299061361</v>
       </c>
       <c r="GA8" t="n">
         <v>-0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.02184476992327926</v>
+        <v>0.03803031142183592</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4982,79 +4982,79 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.0200614072740682</v>
+        <v>-0.1011850256962435</v>
       </c>
       <c r="B9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.123687512704554</v>
+        <v>0.1465154148172163</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06901786037717644</v>
+        <v>-0.08418992946095359</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0007881970371503216</v>
+        <v>0.0033211888094978</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005008680914317614</v>
+        <v>-0.1012851841462958</v>
       </c>
       <c r="K9" t="n">
         <v>-0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06405256431936769</v>
+        <v>0.08862324124550643</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01431297456261952</v>
+        <v>-0.1533319737303613</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.001021781755606933</v>
+        <v>0.005237381019650174</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.01770108146414798</v>
+        <v>0.05987934473344394</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06614390618193003</v>
+        <v>-0.02060067609003889</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06306320790689787</v>
+        <v>-0.1082256165675543</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.06409515106449247</v>
+        <v>0.01596927359673719</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -5063,160 +5063,160 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.02691793788269761</v>
+        <v>0.1276369643566591</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.002102383931987343</v>
+        <v>-0.1211555430546056</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.009110331199949633</v>
+        <v>-0.1778718746463969</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.000128505484707614</v>
+        <v>-0.02322869133937727</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01998668126863742</v>
+        <v>0.05386084604684379</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.01984806016183929</v>
+        <v>-0.104449950175861</v>
       </c>
       <c r="AN9" t="n">
         <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.00609516724211976</v>
+        <v>-0.009630005949965763</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.714980105741063e-05</v>
+        <v>0.01116503729111843</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.005366885824033882</v>
+        <v>-0.1412200994563117</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2726403256107131</v>
+        <v>0.09744951519820724</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.3595756202447056</v>
+        <v>-0.1685792170623614</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06787517267797258</v>
+        <v>0.01801451243507835</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.08806992767766059</v>
+        <v>-0.06181663950393126</v>
       </c>
       <c r="BD9" t="n">
         <v>-0</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.01586659664408104</v>
+        <v>0.03432449815531852</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.06394181716640726</v>
+        <v>0.03556344912818057</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002353456941887972</v>
+        <v>-0.06556255233206885</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0.01280937119687653</v>
+        <v>0.1514593027192798</v>
       </c>
       <c r="BM9" t="n">
         <v>-0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1003800601196751</v>
+        <v>0.03882956770508288</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02378417267946571</v>
+        <v>0.01567193535048356</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0.0101197062645649</v>
+        <v>-0.008458445613486581</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0.008001001745073202</v>
+        <v>-0.04682024802232889</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.1029956880352785</v>
+        <v>0.1227317509295072</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.2345473188879001</v>
+        <v>-0.1168010342249866</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0.02922578286307997</v>
+        <v>0.03169582035214924</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5225,328 +5225,328 @@
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.02543711584607952</v>
+        <v>0.08383698650307268</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0.04500995752376145</v>
+        <v>-0.02640951418251858</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.021892494815779</v>
+        <v>0.09346591102161848</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0007879926858601897</v>
+        <v>0.0007824111171087376</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.007106241718307128</v>
+        <v>-0.01929311303354884</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0.002181094442498632</v>
+        <v>0.00947401597747703</v>
       </c>
       <c r="CP9" t="n">
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.03204467935399882</v>
+        <v>-0.01358007255848504</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.002725843197098776</v>
+        <v>-0.02677514025460652</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.009886167735977683</v>
+        <v>0.08361876861008134</v>
       </c>
       <c r="CW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0.04501037285365359</v>
+        <v>-0.06234071843918215</v>
       </c>
       <c r="CY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.0003843302519835677</v>
+        <v>0.04611417812011365</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.005461835551664755</v>
+        <v>0.004579670029474124</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.03496121544751814</v>
+        <v>-0.02753748011088676</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0.04936431175715914</v>
+        <v>-0.02867264901366889</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08271037929897325</v>
+        <v>0.1195666362707087</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0354628568550487</v>
+        <v>-0.003616339543478052</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.07245223494298547</v>
+        <v>-0.1041351385785861</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.02221975825620794</v>
+        <v>0.02864691583641713</v>
       </c>
       <c r="DQ9" t="n">
         <v>-0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.003065796825661416</v>
+        <v>-0.1018596765387029</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.03160939188435875</v>
+        <v>0.002749593299139978</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0.01196350767535276</v>
+        <v>0.01030080129641001</v>
       </c>
       <c r="DX9" t="n">
         <v>-0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.02110137241035536</v>
+        <v>0.1974821315519447</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.0911788166699757</v>
+        <v>-0.2434674052436188</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0.01763952051516446</v>
+        <v>0.04338011864846494</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0.006260338043776301</v>
+        <v>0.08609292979397715</v>
       </c>
       <c r="EG9" t="n">
         <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0.1032090373981176</v>
+        <v>-0.01617044680172869</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.001464958599625886</v>
+        <v>0.0183806110829547</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0.02640718397602952</v>
+        <v>0.05540403822731108</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.04730680147221221</v>
+        <v>0.02222459974140883</v>
       </c>
       <c r="EP9" t="n">
         <v>0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0.03011728941635672</v>
+        <v>0.09864659902458277</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.05885040451933026</v>
+        <v>0.01625927228302161</v>
       </c>
       <c r="ET9" t="n">
         <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0.06129726515050925</v>
+        <v>0.02551315814802336</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.01142969467311233</v>
+        <v>0.08356069269141161</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0.04539034034244956</v>
+        <v>-0.06965622017861062</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.01186955825652294</v>
+        <v>0.07804696586168841</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0.00119627445104718</v>
+        <v>-0.005962827604597895</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.03136579989725725</v>
+        <v>0.2819669771339198</v>
       </c>
       <c r="FH9" t="n">
         <v>0</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0.01285018867011167</v>
+        <v>-0.005236536963853613</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03724626192695479</v>
+        <v>0.01304388730425286</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0.08138919059275386</v>
+        <v>0.07102595327806149</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.02945418296582816</v>
+        <v>0.2605224317211582</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.06336037823983036</v>
+        <v>-0.2004490743850912</v>
       </c>
       <c r="FS9" t="n">
         <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.05799947540881113</v>
+        <v>0.1204540628809419</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0.04340488558826013</v>
+        <v>0.02396071678706651</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0.01753598711772844</v>
+        <v>0.1660644403332305</v>
       </c>
       <c r="FZ9" t="n">
         <v>-0</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.02886999045069499</v>
+        <v>-0.06475574414565183</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>-0.04651275654993939</v>
+        <v>0.07162680616957169</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,106 +5554,106 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08351118452251841</v>
+        <v>0.4003565156345584</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01320123793118527</v>
+        <v>0.01273855608248268</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04529023093832909</v>
+        <v>-0.2339379126128109</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06535983986938539</v>
+        <v>0.4192551276994853</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.006793900127755191</v>
+        <v>-0.1117312194284471</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.03322488220039907</v>
+        <v>-0.1702700312248493</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009822764705973853</v>
+        <v>0.006124024067210783</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0234344345780879</v>
+        <v>-0.1108154260925916</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01308707002315567</v>
+        <v>-0.1278911556380632</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01756979870404508</v>
+        <v>0.1672616446192672</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01567553770960045</v>
+        <v>-0.07194757280138428</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0180788109139705</v>
+        <v>0.04508528251306015</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01237807951541193</v>
+        <v>0.1907087111294614</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0085290956322954</v>
+        <v>0.02329944264130236</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.04158299724169656</v>
+        <v>-0.1855309793097825</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,55 +5686,55 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1095804369729856</v>
+        <v>0.7863156536486945</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.0005527761491386364</v>
+        <v>-0.3408042510374893</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.07205021174801415</v>
+        <v>-0.303955333020439</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04926608610865383</v>
+        <v>0.0876836710213962</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.04050711410312836</v>
+        <v>0.01502740615966631</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.03395251379719318</v>
+        <v>-0.2475437200102016</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,34 +5743,34 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03137093675354004</v>
+        <v>0.1120219369508415</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01523320100554269</v>
+        <v>0.1337034471319601</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.006006186475346823</v>
+        <v>0.1300288963146143</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04511639881342314</v>
+        <v>0.3769486959635328</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,13 +5779,13 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.006382651962499497</v>
+        <v>-0.1247576657460409</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.02999523669751284</v>
+        <v>-0.3111041369809541</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.0281772336841882</v>
+        <v>-0.280597385271228</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,40 +5806,40 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0006109525250054642</v>
+        <v>-0.02007116624803969</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02186702591063006</v>
+        <v>0.2023545496962904</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.001911732396497594</v>
+        <v>-0.09192033803824559</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001752574295650408</v>
+        <v>0.03142727063467615</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.003588829407028833</v>
+        <v>0.04338447998343203</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
@@ -5848,22 +5848,22 @@
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02463680078627102</v>
+        <v>-0.2632351385231388</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.001635210163524141</v>
+        <v>-0.02763515786342295</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02712245475220463</v>
+        <v>0.1802576568505767</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
@@ -5878,19 +5878,19 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.007668707833058857</v>
+        <v>-0.03785764155485199</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01776238444645639</v>
+        <v>-0.05338220482039615</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.01921709120848792</v>
+        <v>0.1213730200908449</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5899,25 +5899,25 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01117876900012673</v>
+        <v>-0.111390597734001</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03498660255857731</v>
+        <v>-0.03882878550356052</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.000307458152089656</v>
+        <v>0.06576320348197498</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03312167976367825</v>
+        <v>0.1011874926898632</v>
       </c>
       <c r="DY10" t="n">
         <v>-0</v>
@@ -5941,10 +5941,10 @@
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.02521882341374234</v>
+        <v>-0.01138402813949212</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0005588012438533462</v>
+        <v>0.03205766769109054</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
@@ -5953,94 +5953,94 @@
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02554732555925535</v>
+        <v>-0.1077693080223029</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.00242138290969484</v>
+        <v>-0.1134466885956163</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01071862170761232</v>
+        <v>0.1848458968759943</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.02288261265100248</v>
+        <v>-0.1741626899405963</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01930744017635391</v>
+        <v>-0.1456697451912187</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.02088257970534594</v>
+        <v>0.1354334777959573</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02582541546675255</v>
+        <v>-0.283869978619706</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.00296276761879366</v>
+        <v>-0.06946340823309152</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02676432626969752</v>
+        <v>0.1826905698587204</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.004812079215437747</v>
+        <v>-0.2017023058346216</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
@@ -6049,13 +6049,13 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02768011233511165</v>
+        <v>0.1043529771139708</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.03047259253457564</v>
+        <v>0.2047243100475794</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
         <v>0</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01496675846669518</v>
+        <v>-0.07634467348486192</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,46 +6076,46 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.004090271518550663</v>
+        <v>0.1032960670922323</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.0009483440502148785</v>
+        <v>-0.00694019616801537</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01848853436980121</v>
+        <v>-0.1042858288908992</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.01533550378706776</v>
+        <v>0.09390879306237204</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,16 +6123,16 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.367790117989166</v>
+        <v>0.3011416932842322</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1679093473262172</v>
+        <v>-0.2167665405949165</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0853951589193948</v>
+        <v>-0.0470129648676311</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6150,16 +6150,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3141038396398625</v>
+        <v>0.3044606086623222</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.09415458487549362</v>
+        <v>-0.1971766253030765</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.09540120256546557</v>
+        <v>-0.08387706769624097</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6171,82 +6171,82 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1111258555446107</v>
+        <v>0.07058787976404382</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.03528980161732149</v>
+        <v>-0.01501027447945392</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05554817873500196</v>
+        <v>-0.140443942129446</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1220105025594596</v>
+        <v>0.09015852555826334</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01621040198305509</v>
+        <v>-0.1130753419810819</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.05985970366858973</v>
+        <v>-0.126588421325469</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.05226958194249584</v>
+        <v>0.2252261989249789</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.0898665107534376</v>
+        <v>-0.09414979467469463</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.08470723602345487</v>
+        <v>0.06483978442973869</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6258,16 +6258,16 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5562495647275811</v>
+        <v>0.4826563815541924</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.08332993168348901</v>
+        <v>-0.1912144745521153</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.07591353231710352</v>
+        <v>-0.2945512938623024</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6282,19 +6282,19 @@
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05112183445036298</v>
+        <v>-0.03662726175581003</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.07459694144106048</v>
+        <v>-0.01042591873001647</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1651643886690285</v>
+        <v>-0.07048140012064701</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,16 +6312,16 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06286626752881233</v>
+        <v>0.002408515276528257</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.1068369317530743</v>
+        <v>0.06514252384785732</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1300910455940907</v>
+        <v>0.1088235937888509</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
@@ -6330,79 +6330,79 @@
         <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.3036379445129308</v>
+        <v>0.2536467620396329</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.03967474353103857</v>
+        <v>-0.1345752610718376</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.06351267356854493</v>
+        <v>-0.05959255086479163</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1135618671765013</v>
+        <v>-0.1977713058848711</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.04497337883135222</v>
+        <v>0.1973314257182044</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.0002104958428571662</v>
+        <v>0.03988285385512216</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.02128972765494081</v>
+        <v>-0.04317806249903525</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.05691725408631867</v>
+        <v>0.2219974962696549</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.04707347711396828</v>
+        <v>0.03294058185658881</v>
       </c>
       <c r="CR11" t="n">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
@@ -6420,70 +6420,70 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1086398100401987</v>
+        <v>-0.1790312863318097</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.06485736319129738</v>
+        <v>0.2123642513085991</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.00626434301985177</v>
+        <v>0.04961661557195554</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.004448116044358633</v>
+        <v>-0.05215405107181421</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.1754694621157778</v>
+        <v>0.08310860755720594</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.003577512789650971</v>
+        <v>-0.02569137554925148</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.08859621319188885</v>
+        <v>-0.1011520374342138</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.06445856086044234</v>
+        <v>0.1731071196476971</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.1020173123144329</v>
+        <v>-0.05903063653798989</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
@@ -6492,25 +6492,25 @@
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.1016237707676746</v>
+        <v>-0.154251479639796</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.04030076098166258</v>
+        <v>-0.1207375466924777</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0285996344048736</v>
+        <v>-0.1063340322065107</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
@@ -6519,25 +6519,25 @@
         <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1055290520349488</v>
+        <v>-0.0826023427401346</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.08353292079833716</v>
+        <v>0.1551515371600857</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.1156632752252773</v>
+        <v>0.07209582432596823</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6546,31 +6546,31 @@
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1077098632328069</v>
+        <v>-0.1590089012190171</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.06116759317860897</v>
+        <v>0.0999649974924091</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.02049875390171084</v>
+        <v>0.05507774790800651</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,79 +6579,79 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.106962014915616</v>
+        <v>-0.2061296696251358</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.07774094759721513</v>
+        <v>0.2155000076207586</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.01569718117715356</v>
+        <v>0.02117705936242639</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.08190430328516339</v>
+        <v>-0.01901706370314471</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.06948109600871664</v>
+        <v>0.06195156588260993</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02746744619331716</v>
+        <v>-0.1124321292376229</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0299328486599257</v>
+        <v>0.01148103334189972</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.03975663463777522</v>
+        <v>-0.03935861903249632</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.06592335199628245</v>
+        <v>0.03459183123541374</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
@@ -6660,16 +6660,16 @@
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05471568911768196</v>
+        <v>-0.09245331478305342</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.000217316402211568</v>
+        <v>0.1277291232532143</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
@@ -6681,15 +6681,15 @@
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1083619176166803</v>
+        <v>0.09619710659188101</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -6698,25 +6698,25 @@
         <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09949598167393674</v>
+        <v>-0.1809421907177333</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06218267043558526</v>
+        <v>0.01392000816902382</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1136815600324153</v>
+        <v>0.05606627293602472</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -6725,10 +6725,10 @@
         <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03140935815771556</v>
+        <v>-0.2236857091464473</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01994970954349517</v>
+        <v>-0.02670983490341289</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,10 +6740,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02323991262373931</v>
+        <v>-0.01627714798907641</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -6752,40 +6752,40 @@
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05894649898217037</v>
+        <v>-0.05470386364303211</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06158050611337822</v>
+        <v>-0.03897772861555988</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.02489383988355754</v>
+        <v>0.009781602095894303</v>
       </c>
       <c r="AC12" t="n">
         <v>-0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.02180323123357347</v>
+        <v>0.07439872021011142</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.04505967239497784</v>
+        <v>0.1748293364457923</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -6794,49 +6794,49 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.01352927843214914</v>
+        <v>0.02277277539628697</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01713655448449533</v>
+        <v>-0.1597992637780607</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.07614006159606133</v>
+        <v>0.06454126720507015</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>-0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.1029617644083419</v>
+        <v>-0.04895992948811435</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.09508939973776327</v>
+        <v>-0.3430717157063762</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.154165223212914</v>
+        <v>-0.04925271240581177</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,7 +6851,7 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.1156866883522148</v>
+        <v>0.1635764989378813</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -6860,37 +6860,37 @@
         <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.007244516735436311</v>
+        <v>0.2325887610159582</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.05498929656676175</v>
+        <v>0.1364718135498603</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.05847714844719504</v>
+        <v>0.02090477178077167</v>
       </c>
       <c r="BM12" t="n">
         <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02056980535060678</v>
+        <v>0.01338018747989064</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1219040145916195</v>
+        <v>-0.1160443397549065</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -6899,25 +6899,25 @@
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.04411232746682719</v>
+        <v>-0.0644191222532786</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.008070997770495887</v>
+        <v>-0.2641327945217364</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07151953808421369</v>
+        <v>-0.02787965379276942</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -6926,25 +6926,25 @@
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>-0.02793851621626495</v>
+        <v>-0.05791980675901579</v>
       </c>
       <c r="CE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.01005652658307802</v>
+        <v>0.1157076599355412</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01985895759682238</v>
+        <v>-0.005949583062802882</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6956,49 +6956,49 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM12" t="n">
-        <v>-0.01471360722727394</v>
+        <v>0.0005146925664979891</v>
       </c>
       <c r="CN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04042062697347008</v>
+        <v>0.07146031261128742</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.0305142041212892</v>
+        <v>-0.03147341785499048</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0.01624575429072344</v>
+        <v>-0.04345260596690531</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.007405887348552478</v>
+        <v>0.1152815778724382</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.005908940683657114</v>
+        <v>0.01292862330814252</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
@@ -7010,10 +7010,10 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0.01515133483721191</v>
+        <v>-0.01687577004601233</v>
       </c>
       <c r="DF12" t="n">
         <v>-0</v>
@@ -7022,13 +7022,13 @@
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1031182216393626</v>
+        <v>0.103073480017947</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.05114043868353677</v>
+        <v>-0.02725695639757577</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7037,106 +7037,106 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0.02439958493730065</v>
+        <v>-0.06775526866602874</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03582175303900088</v>
+        <v>-0.0006842494852552349</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.06222310328364109</v>
+        <v>0.04672097706861199</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0.03381059379722615</v>
+        <v>0.02278480394753791</v>
       </c>
       <c r="DX12" t="n">
         <v>-0</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.03146389451212453</v>
+        <v>0.06332618173357736</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02747839315822766</v>
+        <v>0.01302396191254972</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0.0161531410940369</v>
+        <v>-0.08262996379990607</v>
       </c>
       <c r="EG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0239713736471579</v>
+        <v>0.08576699087656743</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.004694043287578408</v>
+        <v>0.03963129111838749</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>-0.01431831098086163</v>
+        <v>0.02515020627178729</v>
       </c>
       <c r="EP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02322261027676266</v>
+        <v>0.1105419070175937</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02070096440911376</v>
+        <v>0.00799065094468589</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7148,19 +7148,19 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>-0.01674014045021427</v>
+        <v>-0.0500019896129426</v>
       </c>
       <c r="EY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.00241364236008606</v>
+        <v>0.1518792058651048</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01479024501021157</v>
+        <v>0.001844130251671888</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
@@ -7172,10 +7172,10 @@
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0.01831354105287125</v>
+        <v>0.03068072908478866</v>
       </c>
       <c r="FH12" t="n">
         <v>0</v>
@@ -7184,52 +7184,52 @@
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.04217783462030121</v>
+        <v>0.08958414333138043</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1231620280856641</v>
+        <v>0.1239793784650093</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.005457861109323356</v>
+        <v>0.005662700368589849</v>
       </c>
       <c r="FQ12" t="n">
         <v>0</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.01403177682412987</v>
+        <v>0.2199386417806481</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.04748028772958966</v>
+        <v>0.07183676147755857</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0168127154378239</v>
+        <v>0.01513560164138345</v>
       </c>
       <c r="FZ12" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.006259089607539816</v>
+        <v>0.2222442781029189</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -8399,25 +8399,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3903899599068201</v>
+        <v>0.3414751278254324</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.12301158215373</v>
+        <v>-0.1646246902497561</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.04595739902859299</v>
+        <v>-0.04906524876642247</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,16 +8426,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2489137885265292</v>
+        <v>0.3421309317726905</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1614015120650168</v>
+        <v>-0.2371215841573983</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.03996511631588533</v>
+        <v>-0.1211913554100068</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8453,79 +8453,79 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1076452051745882</v>
+        <v>0.05896119103948463</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.008548895634564752</v>
+        <v>-0.08265703254204008</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1182314242278777</v>
+        <v>-0.08694981319262353</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.05007861534100465</v>
+        <v>-0.05300407769609101</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.005051307049637887</v>
+        <v>-0.1590486402882878</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01563131499312967</v>
+        <v>-0.05440129668619219</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.003188633553531933</v>
+        <v>0.1223702725076341</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.06347406846426253</v>
+        <v>-0.1353909442459903</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.05283839352519829</v>
+        <v>0.07355294527851673</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
@@ -8534,25 +8534,25 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.3986812209517081</v>
+        <v>0.333981228891482</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02785754064777585</v>
+        <v>-0.08368883416083876</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1076177021508507</v>
+        <v>-0.2476598984715125</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.07191475447803521</v>
+        <v>-0.005159825729888107</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.1783564486129425</v>
+        <v>-0.03519035217183181</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.113962743301363</v>
+        <v>-0.03512902639527607</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,19 +8588,19 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.09804115347022564</v>
+        <v>0.005747183853558196</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.05243524008936522</v>
+        <v>0.04825910062824774</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.181943580264761</v>
+        <v>0.04969999050112857</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
@@ -8609,103 +8609,103 @@
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1456172790520416</v>
+        <v>0.1949093626766803</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02243908643535936</v>
+        <v>-0.1324977676878812</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.06681098219063472</v>
+        <v>-0.06194993423030137</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1058124429807021</v>
+        <v>-0.1376819764653716</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.00655769013125949</v>
+        <v>0.1268961210950319</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01204887846804626</v>
+        <v>0.01414542966573564</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.002607301453425986</v>
+        <v>-0.05021974804012512</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.07414160928259059</v>
+        <v>0.1543178834079943</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.04699480751126667</v>
+        <v>0.03738294863047781</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.07673071276394879</v>
+        <v>-0.1367517371823849</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.02827050089526687</v>
+        <v>0.1361345454132594</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01740918672576505</v>
+        <v>0.02907320876465089</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,16 +8723,16 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.03295959548477716</v>
+        <v>-0.063803938905398</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.04508779023656104</v>
+        <v>0.03889999214781231</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07856920888315456</v>
+        <v>-0.1224566738530367</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8747,28 +8747,28 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.07829090432631541</v>
+        <v>-0.09319822641289845</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.02319772432131826</v>
+        <v>-0.05143286841619749</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04188563136689308</v>
+        <v>-0.02527432969446518</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
@@ -8777,16 +8777,16 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.090042353871638</v>
+        <v>-0.01312555484851022</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.02046324527388147</v>
+        <v>0.08212191585103511</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01929354801356292</v>
+        <v>-0.02145651393025769</v>
       </c>
       <c r="EB15" t="n">
         <v>-0</v>
@@ -8798,22 +8798,22 @@
         <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.09378312275342719</v>
+        <v>-0.1042661337706217</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01079503310618586</v>
+        <v>0.08984316125214342</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.05908913573862865</v>
+        <v>0.06193008082988396</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
@@ -8822,31 +8822,31 @@
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.009636545691823286</v>
+        <v>-0.03561949360701803</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.003643788556122243</v>
+        <v>0.08159582889176643</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03621695026013591</v>
+        <v>-0.002502705129854616</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,16 +8858,16 @@
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.07613873713411132</v>
+        <v>-0.1495442637604981</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.01288117392737354</v>
+        <v>0.1611629942607687</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01451815516142239</v>
+        <v>0.006986145286889089</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
@@ -8876,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
@@ -8885,16 +8885,16 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.05041508433479705</v>
+        <v>0.134291793115546</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.01073994352231492</v>
+        <v>0.09960204511361992</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0341162963639297</v>
+        <v>0.0167974623518992</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,55 +8906,55 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.05208253936190817</v>
+        <v>0.05842460472388274</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.01234393345489426</v>
+        <v>0.1649794802261243</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.06320378459313053</v>
+        <v>-0.004025112165035588</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06612064879380536</v>
+        <v>-0.0693861540932609</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.1256650544819885</v>
+        <v>0.07774833828509491</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1143279005314649</v>
+        <v>0.2639445486061177</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0345752959621311</v>
+        <v>-0.002052039287393602</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06239134208674955</v>
+        <v>-0.1363755558557626</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09141289130782031</v>
+        <v>0.3112969535020539</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,64 +9004,64 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02705539721881642</v>
+        <v>-0.07253802529589272</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.05394075877106173</v>
+        <v>-0.1554919351923687</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.007383668633417352</v>
+        <v>0.07749701844833358</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.004870207182334208</v>
+        <v>-0.1042055907376616</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01134815328556541</v>
+        <v>-0.01436129577058397</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.005926361470438855</v>
+        <v>-0.01939634972022067</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01753946246891136</v>
+        <v>-0.1865424793530553</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.004496617713269755</v>
+        <v>0.03808647380991899</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -9070,67 +9070,67 @@
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.005408116668790586</v>
+        <v>0.03982980136274061</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01443178168378754</v>
+        <v>-0.02248118409729503</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01146816374266166</v>
+        <v>-0.008036995103033644</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1004971032368545</v>
+        <v>0.291680267469199</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.01470417601279989</v>
+        <v>-0.2074010446376391</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.01849981975790718</v>
+        <v>-0.1039918067938328</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03679904296723396</v>
+        <v>0.0003076142226975543</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,40 +9139,40 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.04858110665900109</v>
+        <v>0.006165456901080113</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.06336061074863006</v>
+        <v>-0.07608243834739747</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03673162805556374</v>
+        <v>0.0371513494818342</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02197255604319858</v>
+        <v>0.08215903874103367</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01721748149928298</v>
+        <v>0.006104407821335978</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
@@ -9181,10 +9181,10 @@
         <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.04087727176391204</v>
+        <v>0.1518925555075795</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.007240033270322955</v>
+        <v>-0.04363818389794966</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.004304945497511532</v>
+        <v>-0.1035077259315777</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,31 +9205,31 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.02319513683937444</v>
+        <v>-0.09126863084934907</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.001271571297277626</v>
+        <v>0.01154915134604646</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02120629473961122</v>
+        <v>0.06176394231955251</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.001623364339564665</v>
+        <v>-0.03513775188119758</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,64 +9247,64 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.003057384995051025</v>
+        <v>0.06753084228527502</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.0120592434677721</v>
+        <v>0.04276206206073455</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01849006580432115</v>
+        <v>-0.09542123410925388</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.00423495222439333</v>
+        <v>0.01015368218915604</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.02069031066948066</v>
+        <v>0.08355343815800995</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.01339827270336243</v>
+        <v>-0.02481430962633647</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02319380428218064</v>
+        <v>-0.09925084258122067</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.006539559999701746</v>
+        <v>0.08150311274070401</v>
       </c>
       <c r="DK16" t="n">
         <v>-0</v>
@@ -9319,76 +9319,76 @@
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.008574837123314744</v>
+        <v>-0.03970863760018473</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01477565445146246</v>
+        <v>-0.07361369644379913</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.006743955129744157</v>
+        <v>0.02853674093840061</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.03686297202444388</v>
+        <v>0.004968984492609236</v>
       </c>
       <c r="DY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01527050619536186</v>
+        <v>-0.03286712947092321</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01042694495183295</v>
+        <v>0.03421614387193686</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.02558768515669901</v>
+        <v>-0.03453901236053829</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.004632485526832495</v>
+        <v>0.01035707474889377</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.01844592223684036</v>
+        <v>0.01839443770418432</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9400,19 +9400,19 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.0116201810240523</v>
+        <v>-0.02479509244159997</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.004522156679603304</v>
+        <v>0.001594248829110724</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.004205640022970201</v>
+        <v>0.08418855559629601</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
@@ -9421,40 +9421,40 @@
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01873082565654385</v>
+        <v>-0.1064781859777357</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.008211932370117431</v>
+        <v>-0.005314095816375085</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02467758441660555</v>
+        <v>0.05668148319542251</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.02305293284529085</v>
+        <v>0.1484297907591597</v>
       </c>
       <c r="FI16" t="n">
         <v>0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.009127348013994034</v>
+        <v>-0.05743848518748069</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01526373180946174</v>
+        <v>0.1150419177600892</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.004324778527337106</v>
+        <v>0.0451989675555321</v>
       </c>
       <c r="FR16" t="n">
         <v>0</v>
@@ -9490,46 +9490,46 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.01835294647580813</v>
+        <v>-0.07666068978336733</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01051016329872418</v>
+        <v>-0.03685305774713382</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.003800622357368355</v>
+        <v>-0.03023233029571476</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.006567268970569907</v>
+        <v>0.09474924070677998</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,25 +9537,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4204248059976881</v>
+        <v>0.2870803796496585</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1513437874573826</v>
+        <v>-0.1401999841712212</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04527633653911799</v>
+        <v>-0.05880413082882723</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2840311894145032</v>
+        <v>0.3148869253823578</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1595070717946975</v>
+        <v>-0.1846699257687953</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04125455865544417</v>
+        <v>-0.1027267281081586</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9591,106 +9591,106 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1089724602982802</v>
+        <v>0.03784756891158361</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01525528896144454</v>
+        <v>-0.04914287600567894</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1029457254037204</v>
+        <v>-0.07919550557583102</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.02564272914483085</v>
+        <v>-0.06066386109802748</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.0003745588774471654</v>
+        <v>-0.1052726986246386</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.01023002877953238</v>
+        <v>-0.06935708733384816</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01614411383958417</v>
+        <v>0.08759351355245774</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.06473810382208256</v>
+        <v>-0.09895867279616775</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.05054100800603232</v>
+        <v>0.04787458278200581</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4200292436198088</v>
+        <v>0.2589648742882208</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.02421297950909617</v>
+        <v>-0.07717367133816133</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.09616729179188384</v>
+        <v>-0.1836385003589411</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,25 +9699,25 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04829735294955435</v>
+        <v>-0.01236214015113974</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.1800723684225316</v>
+        <v>-0.03557856355761192</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1101881038224136</v>
+        <v>-0.01923087052277619</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,19 +9726,19 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1252408629167701</v>
+        <v>-0.002512399369763944</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.05094889780469207</v>
+        <v>0.05856203963465392</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.173138888938276</v>
+        <v>0.04520032783499268</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
         <v>0</v>
@@ -9747,49 +9747,49 @@
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1607959632635502</v>
+        <v>0.14892975125004</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.00767301831449932</v>
+        <v>-0.1015125591368312</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0593762895282619</v>
+        <v>-0.04438393337670463</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.0934363313431307</v>
+        <v>-0.09744577847852978</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.002633074370740935</v>
+        <v>0.09548676626578344</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.01702490342847021</v>
+        <v>0.01600887531436344</v>
       </c>
       <c r="CI17" t="n">
         <v>-0</v>
@@ -9801,31 +9801,31 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.001053046039365513</v>
+        <v>-0.0363888422153778</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.06988428133560742</v>
+        <v>0.1076280593567051</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.06247274175331659</v>
+        <v>0.02362672527814446</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
         <v>-0</v>
@@ -9834,43 +9834,43 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.06412551117234662</v>
+        <v>-0.09748393870834925</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0389127060682261</v>
+        <v>0.1026237506050639</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.02192250431565087</v>
+        <v>0.02441050189639309</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.0456642651849956</v>
+        <v>-0.05755119111223897</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.05037609118490947</v>
+        <v>0.01744981722091394</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02949671395194503</v>
+        <v>-0.03662271232871284</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,28 +9885,28 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.07546151943161547</v>
+        <v>-0.05391450361534146</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.001881425167425937</v>
+        <v>-0.0237432589254039</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.03649671743729348</v>
+        <v>-0.02219148127917356</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,16 +9915,16 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.09959164515694852</v>
+        <v>0.002461758638433556</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.01450911645524525</v>
+        <v>0.06487733641427397</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0336492069458345</v>
+        <v>-0.008379430993075634</v>
       </c>
       <c r="EB17" t="n">
         <v>-0</v>
@@ -9936,85 +9936,85 @@
         <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.08023888852332932</v>
+        <v>-0.07218004013360911</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.0139410408364859</v>
+        <v>0.06851250357117927</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.05840431881777963</v>
+        <v>0.05344243636881892</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.002221591099712645</v>
+        <v>-0.02632851886587431</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>-0.008302098082398967</v>
+        <v>0.06792165506047149</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.02507581397599525</v>
+        <v>-0.0005905644970918748</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.06378486782226957</v>
+        <v>-0.1031937688703947</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>2.957922741352929e-05</v>
+        <v>0.1221173312994944</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.008994425823406172</v>
+        <v>0.004150358425308507</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
         <v>0</v>
@@ -10023,16 +10023,16 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.07137788021175437</v>
+        <v>0.1157121394264769</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0004140648505452317</v>
+        <v>0.0807746817058973</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.04910752532634945</v>
+        <v>0.01101780399065784</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10044,28 +10044,28 @@
         <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.0536832459693065</v>
+        <v>0.02914432841834603</v>
       </c>
       <c r="FR17" t="n">
         <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.01201721965267037</v>
+        <v>0.107565349382176</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.07072742617161869</v>
+        <v>-0.02332317383636093</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>-0</v>
@@ -10074,28 +10074,28 @@
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.06989410873087215</v>
+        <v>-0.05307117605141522</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.1250289337699567</v>
+        <v>0.0391857815258545</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
@@ -10103,10 +10103,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2894394161082995</v>
+        <v>0.4642831961309457</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.06272773670541325</v>
+        <v>0.03623074630007089</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1970526873881512</v>
+        <v>-0.3625694817344876</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
@@ -10130,10 +10130,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2529577685726819</v>
+        <v>0.6073311617702576</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,25 +10142,25 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.01532614662274989</v>
+        <v>-0.1127134590855842</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1673787289095806</v>
+        <v>-0.3952552319449173</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03431218375515149</v>
+        <v>0.1356905721635422</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -10169,40 +10169,40 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.05388440482186044</v>
+        <v>-0.1203496920802387</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0003380747105889077</v>
+        <v>-0.1161351153268603</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.006313879432028153</v>
+        <v>-0.05139541902307491</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.008513386885082547</v>
+        <v>-0.2643866095075427</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.01731525258001359</v>
+        <v>0.1172584325986208</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.05081582990074601</v>
+        <v>0.129102422832732</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.008345866163603987</v>
+        <v>-0.0763880419566956</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.06259298462548103</v>
+        <v>-0.1203382779313333</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,37 +10238,37 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.215003428880374</v>
+        <v>0.7135532866479957</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.05265705925207809</v>
+        <v>-0.3553802254808059</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.1240614613013089</v>
+        <v>-0.305218711242963</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.07902487384554199</v>
+        <v>-0.1208428278970344</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,52 +10277,52 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.0466529314034206</v>
+        <v>0.04848935790244129</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.07499006501205618</v>
+        <v>-0.04705817726294734</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.07205906621350128</v>
+        <v>0.1464209441416096</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02315693790189314</v>
+        <v>0.07753203523104789</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.0236619192036197</v>
+        <v>0.09284635765280942</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1062753071698799</v>
+        <v>0.3341892721612888</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,40 +10331,40 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.03842524791624177</v>
+        <v>-0.04414456173847815</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.05274223512112748</v>
+        <v>-0.2374470870662644</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.05487495237638895</v>
+        <v>-0.1837579104637336</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.00457099123784095</v>
+        <v>0.0480691345453734</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.05749214662602975</v>
+        <v>0.1308395751590836</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,46 +10376,46 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.002592370428712802</v>
+        <v>-0.1631448384104796</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.005585204579090892</v>
+        <v>0.1889596917599584</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.03254439120362418</v>
+        <v>0.02179942098633517</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.04765835534723949</v>
+        <v>-0.1709731432836103</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.002399751209139406</v>
+        <v>0.0383330576369724</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.0605781846708975</v>
+        <v>0.1624548596958321</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10424,25 +10424,25 @@
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.05999230219535372</v>
+        <v>-0.1540383076263596</v>
       </c>
       <c r="DG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.07006668907445621</v>
+        <v>-0.0950670878793909</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.003178046815164703</v>
+        <v>0.03960108177357502</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,13 +10451,13 @@
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01979463998720471</v>
+        <v>-0.1147533108473898</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
@@ -10466,16 +10466,16 @@
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01812652228295333</v>
+        <v>-0.01787536471928866</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.01436936528955318</v>
+        <v>0.1639773088902485</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>0</v>
@@ -10484,46 +10484,46 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.04777977594723639</v>
+        <v>-0.06371997326240578</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.02332704482838688</v>
+        <v>0.1016212316496853</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.03204084598396316</v>
+        <v>0.02230734099455505</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.04985985461284646</v>
+        <v>-0.07697511448906905</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.01375102275292586</v>
+        <v>-0.007364837726004603</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.05848137153872406</v>
+        <v>0.02032055060678339</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
@@ -10532,28 +10532,28 @@
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.03833050928693724</v>
+        <v>-0.0659692268386412</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.02262809151813721</v>
+        <v>-0.09268740583272818</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.01753019713148848</v>
+        <v>-0.03985715117049925</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10565,61 +10565,61 @@
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.04813648625368739</v>
+        <v>-0.2052022790172114</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.001635144426316048</v>
+        <v>0.01251767649707819</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.05939632120926604</v>
+        <v>0.1393410906200585</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.02104038576604316</v>
+        <v>0.145088609649334</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.002079197910498624</v>
+        <v>-0.04752951381032525</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.03330008062226393</v>
+        <v>0.1758513610738974</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.00264669136934909</v>
+        <v>0.08704162988577954</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,37 +10628,37 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.04003371472380347</v>
+        <v>-0.1076862176412727</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.0298696777356297</v>
+        <v>-0.0748650372319833</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.01273077758126946</v>
+        <v>-0.008644129289511479</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.02119894658252979</v>
+        <v>0.2023176837350511</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2253785892991495</v>
+        <v>0.3664721904983531</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,16 +10684,16 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.04831610608764746</v>
+        <v>-0.04312314990372144</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1994797707704922</v>
+        <v>-0.16833873259207</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -10702,7 +10702,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2059389935907304</v>
+        <v>0.466800813495776</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -10711,25 +10711,25 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.01632467127160294</v>
+        <v>-0.1676729165604877</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1562961183984397</v>
+        <v>-0.1829935152436964</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01882362272649376</v>
+        <v>0.106576989647475</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -10738,37 +10738,37 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.03174546072773734</v>
+        <v>-0.1479410143131064</v>
       </c>
       <c r="X19" t="n">
-        <v>0.01311474674859296</v>
+        <v>-0.02733697615600099</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.009568458116634664</v>
+        <v>-0.04624567640813852</v>
       </c>
       <c r="AD19" t="n">
         <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.007551527080151848</v>
+        <v>-0.2495140714085942</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.01426408622627168</v>
+        <v>0.04431860670964144</v>
       </c>
       <c r="AH19" t="n">
         <v>-0</v>
@@ -10783,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.0355786465452822</v>
+        <v>0.02175585266989601</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
@@ -10792,13 +10792,13 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.0122055827182206</v>
+        <v>-0.07062337132293839</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.03223901932777645</v>
+        <v>0.01677320597627843</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
@@ -10807,10 +10807,10 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.1754771791141474</v>
+        <v>0.4589077878090633</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
@@ -10819,16 +10819,16 @@
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.04797061810546669</v>
+        <v>-0.2905893600291887</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.1046831635776663</v>
+        <v>-0.1513011543714834</v>
       </c>
       <c r="AZ19" t="n">
         <v>-0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.05918876041465965</v>
+        <v>-0.02941709513505016</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,52 +10846,52 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.0503456007942489</v>
+        <v>-0.01661284878204177</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.08889778408504366</v>
+        <v>-0.07683550133389211</v>
       </c>
       <c r="BI19" t="n">
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.06137327628111427</v>
+        <v>0.06939272823189459</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
         <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.0173471631861932</v>
+        <v>0.0978416553533835</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.02167255232341908</v>
+        <v>-0.005434237650551905</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
         <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.08050909991215278</v>
+        <v>0.2135625367838729</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
@@ -10900,10 +10900,10 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.02102087843413529</v>
+        <v>-0.07986577643266092</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.03098572173828173</v>
+        <v>-0.07700457692544782</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
@@ -10918,22 +10918,22 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.03823981453653991</v>
+        <v>-0.1153342836623316</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.005606907123537335</v>
+        <v>0.03612745180931801</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.0473987561750122</v>
+        <v>0.05923593309926594</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
@@ -10942,82 +10942,82 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.004209063410682411</v>
+        <v>-0.1220706750643736</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.009133578300687699</v>
+        <v>0.1468161486366894</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0.02572484425228578</v>
+        <v>0.1086296385737419</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.02817099814231602</v>
+        <v>-0.1183837927482776</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.002446336546602636</v>
+        <v>0.02197068365309977</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.04871043442894828</v>
+        <v>0.07965682279643672</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE19" t="n">
         <v>-0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.02768716778894524</v>
+        <v>-0.03747050545345273</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.04829889646540801</v>
+        <v>-0.1878964383476275</v>
       </c>
       <c r="DJ19" t="n">
-        <v>-0.009592616438250878</v>
+        <v>0.02598680808271352</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM19" t="n">
         <v>0</v>
@@ -11026,19 +11026,19 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.003646994129159755</v>
+        <v>-0.007829175141517616</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.01102303541961518</v>
+        <v>-0.0978538114187911</v>
       </c>
       <c r="DS19" t="n">
-        <v>-0.008618925083539199</v>
+        <v>0.08403354068051475</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11047,13 +11047,13 @@
         <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.03477508195789758</v>
+        <v>-0.002354147919776317</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
@@ -11062,10 +11062,10 @@
         <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.008946660413252455</v>
+        <v>-0.01233847977329738</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.01975050368172906</v>
+        <v>0.0369642640365558</v>
       </c>
       <c r="EC19" t="n">
         <v>-0</v>
@@ -11077,25 +11077,25 @@
         <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.04138524167596982</v>
+        <v>-0.0561711583999383</v>
       </c>
       <c r="EH19" t="n">
         <v>0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.003890320766146793</v>
+        <v>0.02237555232515982</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.05661067688800695</v>
+        <v>0.002550673299678976</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
         <v>-0</v>
@@ -11107,61 +11107,61 @@
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.0122809650364383</v>
+        <v>-0.01363893595214136</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
         <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.001178171490690924</v>
+        <v>0.01256855724864241</v>
       </c>
       <c r="ET19" t="n">
-        <v>0.03249582258740443</v>
+        <v>0.1306390754919599</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
         <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.02811395849017266</v>
+        <v>-0.1309526122302436</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.0008701481851505198</v>
+        <v>0.00770675095686304</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.04978394638227077</v>
+        <v>0.04839949773885565</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.0122457567241905</v>
+        <v>0.2154532702112459</v>
       </c>
       <c r="FI19" t="n">
         <v>-0</v>
@@ -11170,16 +11170,16 @@
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.000880712051578802</v>
+        <v>-0.07742167877524385</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.02075392299175243</v>
+        <v>0.1363513235915117</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
@@ -11188,55 +11188,55 @@
         <v>0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.01083798453856245</v>
+        <v>0.08189420627280569</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.02443012579387356</v>
+        <v>-0.1175700797191382</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.01970724154307127</v>
+        <v>-0.04757068208828195</v>
       </c>
       <c r="FV19" t="n">
         <v>-0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.01855136667282703</v>
+        <v>-0.0335172496069672</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
         <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0.02955604312859499</v>
+        <v>0.08123363848564287</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -11244,22 +11244,22 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4770137479157708</v>
+        <v>0.3627863959295335</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1148939230936657</v>
+        <v>-0.3658283082927369</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1941318669618476</v>
+        <v>-0.1277902855011704</v>
       </c>
       <c r="F20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H20" t="n">
         <v>-0</v>
@@ -11271,16 +11271,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3434546989506321</v>
+        <v>0.3432797836614352</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1063006075141662</v>
+        <v>-0.4130963037029617</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1882704432761809</v>
+        <v>-0.2939083702447032</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -11295,28 +11295,28 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1393065109008399</v>
+        <v>0.09286785400493645</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.02416967392302835</v>
+        <v>-0.0609532114416588</v>
       </c>
       <c r="W20" t="n">
-        <v>0.03193259225410628</v>
+        <v>-0.1534471298459122</v>
       </c>
       <c r="X20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -11325,43 +11325,43 @@
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1113671648484575</v>
+        <v>-0.005642553274290914</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.002481789047355199</v>
+        <v>-0.1562033927310313</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.04457788347857793</v>
+        <v>-0.1819144699532504</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.04047051497481057</v>
+        <v>0.1871302874713613</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.07420430174827104</v>
+        <v>-0.1565657268007178</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.08715781807251828</v>
+        <v>-0.03656398129877019</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -11370,31 +11370,31 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.4200567589506963</v>
+        <v>0.3626840652861414</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0.009195471282337988</v>
+        <v>-0.254391917473662</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.01912669444084742</v>
+        <v>-0.5089624245117594</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA20" t="n">
         <v>-0</v>
@@ -11403,19 +11403,19 @@
         <v>-0</v>
       </c>
       <c r="BC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.02801788992004425</v>
+        <v>-0.03098800011526178</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-0.03981054467410042</v>
+        <v>-0.1092094751907356</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.231870609942188</v>
+        <v>0.09757630998111948</v>
       </c>
       <c r="BH20" t="n">
         <v>0</v>
@@ -11424,7 +11424,7 @@
         <v>-0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
@@ -11433,76 +11433,76 @@
         <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.1275800174911871</v>
+        <v>0.1133632035376459</v>
       </c>
       <c r="BN20" t="n">
         <v>-0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.08245480851433898</v>
+        <v>0.1792728553452198</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.1423820459059572</v>
+        <v>0.05010746067129347</v>
       </c>
       <c r="BQ20" t="n">
         <v>-0</v>
       </c>
       <c r="BR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
         <v>-0</v>
       </c>
       <c r="BT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.19068520159601</v>
+        <v>0.2438342538815435</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.009179290569408617</v>
+        <v>-0.175509517223002</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.01338227351541913</v>
+        <v>-0.141777275199988</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB20" t="n">
         <v>-0</v>
       </c>
       <c r="CC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.09578784911615007</v>
+        <v>-0.09765970681810617</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.01152239090889618</v>
+        <v>0.2423029067371269</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.0172320442552269</v>
+        <v>0.04768237308310814</v>
       </c>
       <c r="CI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
@@ -11514,16 +11514,16 @@
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.02503571768736587</v>
+        <v>-0.06675259986637884</v>
       </c>
       <c r="CO20" t="n">
         <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.07910850759658523</v>
+        <v>0.307637651391885</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.04180443768791542</v>
+        <v>0.1160131223346328</v>
       </c>
       <c r="CR20" t="n">
         <v>0</v>
@@ -11532,31 +11532,31 @@
         <v>-0</v>
       </c>
       <c r="CT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.07889854931826429</v>
+        <v>-0.08486213376057797</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.0429952159076677</v>
+        <v>0.257324287852923</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0.01271055767908751</v>
+        <v>0.07949301038737659</v>
       </c>
       <c r="DA20" t="n">
         <v>0</v>
       </c>
       <c r="DB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC20" t="n">
         <v>-0</v>
@@ -11568,22 +11568,22 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.02543727784710853</v>
+        <v>-0.1105655657110309</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0.0003817297295997717</v>
+        <v>-0.02366808697625037</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.05964552660000935</v>
+        <v>-0.1301304376198189</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL20" t="n">
         <v>0</v>
@@ -11595,16 +11595,16 @@
         <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.007967219981296418</v>
+        <v>-0.1212597768174527</v>
       </c>
       <c r="DP20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>-0.1108902949368192</v>
+        <v>0.02485986227493844</v>
       </c>
       <c r="DR20" t="n">
-        <v>-0.05941420881625532</v>
+        <v>0.04716921365230188</v>
       </c>
       <c r="DS20" t="n">
         <v>-0</v>
@@ -11613,7 +11613,7 @@
         <v>-0</v>
       </c>
       <c r="DU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV20" t="n">
         <v>0</v>
@@ -11622,16 +11622,16 @@
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.06500612461221221</v>
+        <v>0.06898457254032241</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>-0.02130481398813911</v>
+        <v>0.1389167731420749</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.06307271428993258</v>
+        <v>-0.06468420102646066</v>
       </c>
       <c r="EB20" t="n">
         <v>0</v>
@@ -11640,58 +11640,58 @@
         <v>0</v>
       </c>
       <c r="ED20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF20" t="n">
         <v>0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.102926023348128</v>
+        <v>-0.03430801022946275</v>
       </c>
       <c r="EH20" t="n">
         <v>0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.04959038482142414</v>
+        <v>0.2084241702752791</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.10452818304591</v>
+        <v>0.04800733681302694</v>
       </c>
       <c r="EK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.0634157445003265</v>
+        <v>-0.05288658217477539</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER20" t="n">
-        <v>-0.0673545856323098</v>
+        <v>-0.1912913461553254</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.00152215334852262</v>
+        <v>-0.01855854894706647</v>
       </c>
       <c r="ET20" t="n">
         <v>0</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
         <v>0</v>
@@ -11700,25 +11700,25 @@
         <v>-0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.07601327212569539</v>
+        <v>-0.1176433041046335</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.02513929133019509</v>
+        <v>0.2805456784886066</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.02616955709578965</v>
+        <v>0.03432728993503896</v>
       </c>
       <c r="FC20" t="n">
         <v>-0</v>
       </c>
       <c r="FD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE20" t="n">
         <v>0</v>
@@ -11727,19 +11727,19 @@
         <v>0</v>
       </c>
       <c r="FG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>-0.0383045008335343</v>
+        <v>0.127080364921069</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.08091171618335959</v>
+        <v>0.1785398269742564</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.01524660538992556</v>
+        <v>-0.03127356308787192</v>
       </c>
       <c r="FL20" t="n">
         <v>-0</v>
@@ -11748,61 +11748,61 @@
         <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>-0.01395517148414643</v>
+        <v>0.02987579713298386</v>
       </c>
       <c r="FR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.07277350755058896</v>
+        <v>0.2571349788445131</v>
       </c>
       <c r="FT20" t="n">
-        <v>-0.00354926506275055</v>
+        <v>-0.09128114745804904</v>
       </c>
       <c r="FU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW20" t="n">
         <v>0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.03090909138023808</v>
+        <v>0.03665094752002258</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
-        <v>-0.06116386426559875</v>
+        <v>0.1618597860739516</v>
       </c>
       <c r="GC20" t="n">
         <v>-0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE20" t="n">
         <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
         <v>-0</v>
@@ -11810,10 +11810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.9093879878962898</v>
+        <v>-0.3762755506703589</v>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
@@ -11822,13 +11822,13 @@
         <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.232506657679738</v>
+        <v>0.1366739887927662</v>
       </c>
       <c r="F21" t="n">
-        <v>1.188889548651871</v>
+        <v>0.6221953783223279</v>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -11837,10 +11837,10 @@
         <v>-0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6993961603577442</v>
+        <v>-0.5045066522724956</v>
       </c>
       <c r="L21" t="n">
         <v>-0</v>
@@ -11849,52 +11849,52 @@
         <v>-0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.00590849325265335</v>
+        <v>0.1877242516115198</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8745234788818927</v>
+        <v>0.7494844715763033</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.07855129135503815</v>
+        <v>-0.1444147284010809</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V21" t="n">
         <v>-0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2077519215346388</v>
+        <v>0.1172064824568331</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1441736727648517</v>
+        <v>0.1008660847894718</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.01277405827463008</v>
+        <v>0.02494911092853153</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -11903,10 +11903,10 @@
         <v>-0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.1407474368859606</v>
+        <v>0.2568362468908875</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1432579786650472</v>
+        <v>-0.04631891743824829</v>
       </c>
       <c r="AH21" t="n">
         <v>-0</v>
@@ -11921,7 +11921,7 @@
         <v>-0</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.1018340942625479</v>
+        <v>-0.05980035767356391</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -11930,13 +11930,13 @@
         <v>-0</v>
       </c>
       <c r="AO21" t="n">
-        <v>-0.04158759264748613</v>
+        <v>0.01677070270344581</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.2517824122892482</v>
+        <v>0.1168199180462979</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -11948,34 +11948,34 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>-0.5766830689665847</v>
+        <v>-0.7197691444594455</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW21" t="n">
         <v>-0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.1967671576988113</v>
+        <v>0.08068285222555749</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.7095162522290925</v>
+        <v>0.5326166748058312</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD21" t="n">
-        <v>-0.2703833326096929</v>
+        <v>0.2155463927870517</v>
       </c>
       <c r="BE21" t="n">
         <v>-0</v>
@@ -11984,10 +11984,10 @@
         <v>-0</v>
       </c>
       <c r="BG21" t="n">
-        <v>0.1784293272150296</v>
+        <v>0.1465174494630615</v>
       </c>
       <c r="BH21" t="n">
-        <v>0.354941573882213</v>
+        <v>-0.05630329214409781</v>
       </c>
       <c r="BI21" t="n">
         <v>-0</v>
@@ -11996,31 +11996,31 @@
         <v>0</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM21" t="n">
-        <v>-0.2370140727149798</v>
+        <v>-0.2035219860092397</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>-0.1088535434971289</v>
+        <v>-0.1616004468771174</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0.01930461383751863</v>
+        <v>-0.0862485052473816</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT21" t="n">
         <v>-0</v>
@@ -12029,19 +12029,19 @@
         <v>0</v>
       </c>
       <c r="BV21" t="n">
-        <v>-0.4245591772887607</v>
+        <v>-0.3901776414862667</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX21" t="n">
         <v>-0</v>
       </c>
       <c r="BY21" t="n">
-        <v>0.05683060035236551</v>
+        <v>-0.004403761385673011</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.3655411713818087</v>
+        <v>0.3068968535593723</v>
       </c>
       <c r="CA21" t="n">
         <v>0</v>
@@ -12050,28 +12050,28 @@
         <v>0</v>
       </c>
       <c r="CC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD21" t="n">
         <v>-0</v>
       </c>
       <c r="CE21" t="n">
-        <v>0.1632365940662636</v>
+        <v>0.1274757145914218</v>
       </c>
       <c r="CF21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG21" t="n">
         <v>0</v>
       </c>
       <c r="CH21" t="n">
-        <v>-0.04262249618360861</v>
+        <v>-0.08447556096037678</v>
       </c>
       <c r="CI21" t="n">
-        <v>-0.1847048298283301</v>
+        <v>-0.1598392515930929</v>
       </c>
       <c r="CJ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK21" t="n">
         <v>-0</v>
@@ -12083,7 +12083,7 @@
         <v>-0</v>
       </c>
       <c r="CN21" t="n">
-        <v>0.06257059164901037</v>
+        <v>0.2191370206429023</v>
       </c>
       <c r="CO21" t="n">
         <v>0</v>
@@ -12092,40 +12092,40 @@
         <v>0</v>
       </c>
       <c r="CQ21" t="n">
-        <v>-0.1141478405480383</v>
+        <v>-0.05716289660925816</v>
       </c>
       <c r="CR21" t="n">
-        <v>0.04082169286726398</v>
+        <v>-0.02010829265149674</v>
       </c>
       <c r="CS21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV21" t="n">
         <v>0</v>
       </c>
       <c r="CW21" t="n">
-        <v>0.1427036687356383</v>
+        <v>0.1254094183056176</v>
       </c>
       <c r="CX21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY21" t="n">
         <v>-0</v>
       </c>
       <c r="CZ21" t="n">
-        <v>-0.05069386907686284</v>
+        <v>-0.07946283916363373</v>
       </c>
       <c r="DA21" t="n">
-        <v>-0.2100231646329468</v>
+        <v>-0.1904797925279924</v>
       </c>
       <c r="DB21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC21" t="n">
         <v>0</v>
@@ -12134,106 +12134,106 @@
         <v>-0</v>
       </c>
       <c r="DE21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>-0.02658192308571937</v>
+        <v>-0.01988031025108473</v>
       </c>
       <c r="DG21" t="n">
         <v>0</v>
       </c>
       <c r="DH21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI21" t="n">
-        <v>-0.250668625764182</v>
+        <v>0.07634899815915155</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.002352681566828772</v>
+        <v>-0.01555053660299053</v>
       </c>
       <c r="DK21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL21" t="n">
         <v>-0</v>
       </c>
       <c r="DM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO21" t="n">
-        <v>0.04860529194592305</v>
+        <v>-0.01966816481353377</v>
       </c>
       <c r="DP21" t="n">
         <v>-0</v>
       </c>
       <c r="DQ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR21" t="n">
-        <v>-0.03487466333202116</v>
+        <v>0.03603664256036467</v>
       </c>
       <c r="DS21" t="n">
-        <v>-0.1401010338751676</v>
+        <v>-0.1652584089592558</v>
       </c>
       <c r="DT21" t="n">
         <v>0</v>
       </c>
       <c r="DU21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV21" t="n">
         <v>0</v>
       </c>
       <c r="DW21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>0.148259190566158</v>
+        <v>0.1792595299923812</v>
       </c>
       <c r="DY21" t="n">
         <v>0</v>
       </c>
       <c r="DZ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA21" t="n">
-        <v>-0.1046363244900451</v>
+        <v>-0.01770826554789001</v>
       </c>
       <c r="EB21" t="n">
-        <v>-0.0531465382046586</v>
+        <v>-0.0114750988938046</v>
       </c>
       <c r="EC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED21" t="n">
         <v>-0</v>
       </c>
       <c r="EE21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF21" t="n">
         <v>-0</v>
       </c>
       <c r="EG21" t="n">
-        <v>0.1318018175709088</v>
+        <v>0.0482629489488784</v>
       </c>
       <c r="EH21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ21" t="n">
-        <v>-0.1011228755491716</v>
+        <v>-0.02629774547893927</v>
       </c>
       <c r="EK21" t="n">
-        <v>-0.1730308888326496</v>
+        <v>-0.04109785699125441</v>
       </c>
       <c r="EL21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM21" t="n">
         <v>0</v>
@@ -12245,7 +12245,7 @@
         <v>-0</v>
       </c>
       <c r="EP21" t="n">
-        <v>0.1084214411099198</v>
+        <v>0.03864007773240619</v>
       </c>
       <c r="EQ21" t="n">
         <v>0</v>
@@ -12254,25 +12254,25 @@
         <v>-0</v>
       </c>
       <c r="ES21" t="n">
-        <v>-0.03808007117377177</v>
+        <v>-0.06919813107361089</v>
       </c>
       <c r="ET21" t="n">
-        <v>-0.02416250336291188</v>
+        <v>0.1028903804250821</v>
       </c>
       <c r="EU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV21" t="n">
         <v>-0</v>
       </c>
       <c r="EW21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX21" t="n">
         <v>-0</v>
       </c>
       <c r="EY21" t="n">
-        <v>0.1400722209398755</v>
+        <v>0.1485978826336345</v>
       </c>
       <c r="EZ21" t="n">
         <v>0</v>
@@ -12281,13 +12281,13 @@
         <v>0</v>
       </c>
       <c r="FB21" t="n">
-        <v>-0.07190335747186184</v>
+        <v>-0.04081275380392288</v>
       </c>
       <c r="FC21" t="n">
-        <v>-0.1853751458280493</v>
+        <v>-0.1702077730697343</v>
       </c>
       <c r="FD21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE21" t="n">
         <v>-0</v>
@@ -12299,19 +12299,19 @@
         <v>-0</v>
       </c>
       <c r="FH21" t="n">
-        <v>0.01736513147472946</v>
+        <v>-0.0863143082846709</v>
       </c>
       <c r="FI21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ21" t="n">
         <v>0</v>
       </c>
       <c r="FK21" t="n">
-        <v>-0.008163587465345864</v>
+        <v>0.01760356813320094</v>
       </c>
       <c r="FL21" t="n">
-        <v>-0.1528277381078213</v>
+        <v>-0.1504044815107553</v>
       </c>
       <c r="FM21" t="n">
         <v>-0</v>
@@ -12323,10 +12323,10 @@
         <v>-0</v>
       </c>
       <c r="FP21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ21" t="n">
-        <v>-0.0273558575094162</v>
+        <v>0.01635951038461029</v>
       </c>
       <c r="FR21" t="n">
         <v>0</v>
@@ -12335,46 +12335,46 @@
         <v>0</v>
       </c>
       <c r="FT21" t="n">
-        <v>0.08311929548888693</v>
+        <v>0.1347886045256703</v>
       </c>
       <c r="FU21" t="n">
-        <v>-0.1465283862614731</v>
+        <v>0.1765499712909096</v>
       </c>
       <c r="FV21" t="n">
         <v>0</v>
       </c>
       <c r="FW21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX21" t="n">
         <v>-0</v>
       </c>
       <c r="FY21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ21" t="n">
-        <v>-0.01254798392494556</v>
+        <v>0.06960999562667283</v>
       </c>
       <c r="GA21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB21" t="n">
         <v>0</v>
       </c>
       <c r="GC21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.09476902750726415</v>
+        <v>-0.125332831278315</v>
       </c>
       <c r="GE21" t="n">
         <v>0</v>
       </c>
       <c r="GF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
